--- a/pipeline/credit_rating/output/saigonratings_xhtn_20260922.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20260922.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -640,7 +640,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15875,7 +15875,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17282,7 +17282,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17483,7 +17483,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18220,7 +18220,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19292,7 +19292,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19761,7 +19761,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19962,7 +19962,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20230,7 +20230,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20766,7 +20766,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20900,7 +20900,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21168,7 +21168,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21369,7 +21369,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21570,7 +21570,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21704,7 +21704,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21771,7 +21771,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21905,7 +21905,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S327" t="inlineStr"/>
@@ -22541,7 +22541,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S328" t="inlineStr"/>
@@ -22590,7 +22590,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S329" t="inlineStr"/>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-09-22 08:47:13</t>
+          <t>2026-09-22 13:36:45</t>
         </is>
       </c>
       <c r="S330" t="inlineStr"/>
